--- a/artfynd/A 55899-2023 artfynd.xlsx
+++ b/artfynd/A 55899-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55899-2023 artfynd.xlsx
+++ b/artfynd/A 55899-2023 artfynd.xlsx
@@ -2889,7 +2889,7 @@
         <v>112657465</v>
       </c>
       <c r="B21" t="n">
-        <v>56623</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571407</v>
+        <v>571408</v>
       </c>
       <c r="R21" t="n">
         <v>6692740</v>

--- a/artfynd/A 55899-2023 artfynd.xlsx
+++ b/artfynd/A 55899-2023 artfynd.xlsx
@@ -2889,7 +2889,7 @@
         <v>112657465</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 55899-2023 artfynd.xlsx
+++ b/artfynd/A 55899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95269787</v>
+        <v>95271571</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571259.5134806792</v>
+        <v>571283</v>
       </c>
       <c r="R2" t="n">
-        <v>6692752.771030238</v>
+        <v>6692711</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,7 +747,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,12 +757,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>9 blommor, 100-tal bladrosetter</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95271571</v>
+        <v>95271671</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571283.1487487103</v>
+        <v>571256</v>
       </c>
       <c r="R3" t="n">
-        <v>6692710.18292877</v>
+        <v>6692719</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95271671</v>
+        <v>95274252</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571255.7135614039</v>
+        <v>571287</v>
       </c>
       <c r="R4" t="n">
-        <v>6692719.047179565</v>
+        <v>6692705</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95269633</v>
+        <v>95337982</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571219.246284088</v>
+        <v>571335</v>
       </c>
       <c r="R5" t="n">
-        <v>6692784.146500096</v>
+        <v>6692663</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95274252</v>
+        <v>96481182</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,21 +1140,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Killingberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571287.2095226152</v>
+        <v>571265</v>
       </c>
       <c r="R6" t="n">
-        <v>6692705.314076382</v>
+        <v>6692736</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,77 +1194,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson, Åke Persson, Elisabeth Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95270240</v>
+        <v>96481186</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Killingberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571343.3734917776</v>
+        <v>571278</v>
       </c>
       <c r="R7" t="n">
-        <v>6692747.982822844</v>
+        <v>6692712</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,27 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>10 blommor, 100-tal bladrosetter</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,77 +1296,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson, Åke Persson, Elisabeth Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95269698</v>
+        <v>112657442</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571216.0299875716</v>
+        <v>571236</v>
       </c>
       <c r="R8" t="n">
-        <v>6692771.217710961</v>
+        <v>6692739</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,22 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,55 +1412,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95269753</v>
+        <v>112657443</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571244.2326529837</v>
+        <v>571257</v>
       </c>
       <c r="R9" t="n">
-        <v>6692773.749652563</v>
+        <v>6692748</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,27 +1477,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:14</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>200-tal bladrosetter</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,55 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95269649</v>
+        <v>112657444</v>
       </c>
       <c r="B10" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571222.2384385014</v>
+        <v>571258</v>
       </c>
       <c r="R10" t="n">
-        <v>6692783.215445297</v>
+        <v>6692742</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,22 +1574,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,54 +1606,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95336431</v>
+        <v>112657445</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571307.4488697062</v>
+        <v>571242</v>
       </c>
       <c r="R11" t="n">
-        <v>6692810.617282905</v>
+        <v>6692725</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,22 +1671,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,15 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95337982</v>
+        <v>112657446</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,21 +1732,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571334.6380991956</v>
+        <v>571241</v>
       </c>
       <c r="R12" t="n">
-        <v>6692662.697498793</v>
+        <v>6692737</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,22 +1768,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,54 +1800,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95337956</v>
+        <v>112657447</v>
       </c>
       <c r="B13" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1958</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571334.6380991956</v>
+        <v>571236</v>
       </c>
       <c r="R13" t="n">
-        <v>6692662.697498793</v>
+        <v>6692730</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,29 +1865,19 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -2068,55 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95336462</v>
+        <v>112792830</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Igeltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571236.3440065333</v>
+        <v>571311</v>
       </c>
       <c r="R14" t="n">
-        <v>6692771.615710426</v>
+        <v>6692752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,27 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,71 +1982,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95336369</v>
+        <v>117182940</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571371.0907208954</v>
+        <v>571250</v>
       </c>
       <c r="R15" t="n">
-        <v>6692775.248268969</v>
+        <v>6692733</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2263,27 +2059,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>30-tal bladrosetter, 1 blomma</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,15 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96481186</v>
+        <v>117182941</v>
       </c>
       <c r="B16" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,23 +2120,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Killingberget, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571277.6597605092</v>
+        <v>571388</v>
       </c>
       <c r="R16" t="n">
-        <v>6692712.054695751</v>
+        <v>6692681</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,22 +2156,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,34 +2170,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson, Åke Persson, Elisabeth Norman</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96481182</v>
+        <v>112657481</v>
       </c>
       <c r="B17" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,41 +2199,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Killingberget, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571264.7978275444</v>
+        <v>571394</v>
       </c>
       <c r="R17" t="n">
-        <v>6692736.049967805</v>
+        <v>6692828</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,22 +2253,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,27 +2274,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson, Åke Persson, Elisabeth Norman</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96490131</v>
+        <v>112657458</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,45 +2297,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Igeltjärn ö, Eret, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571232.9401060492</v>
+        <v>571231</v>
       </c>
       <c r="R18" t="n">
-        <v>6692692.373964035</v>
+        <v>6692720</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2622,27 +2351,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>födosökningshål i torrgran, stubbe</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,12 +2371,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elisabeth Norman</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elisabeth Norman</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2672,12 +2386,7 @@
         <v>112657461</v>
       </c>
       <c r="B19" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2421,7 @@
         <v>571396</v>
       </c>
       <c r="R19" t="n">
-        <v>6692669</v>
+        <v>6692670</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2771,62 +2480,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112657490</v>
+        <v>117182943</v>
       </c>
       <c r="B20" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571274</v>
+        <v>571388</v>
       </c>
       <c r="R20" t="n">
-        <v>6692739</v>
+        <v>6692669</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2853,12 +2545,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,7 +2559,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2886,15 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112657465</v>
+        <v>117182944</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,42 +2588,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571408</v>
+        <v>571434</v>
       </c>
       <c r="R21" t="n">
-        <v>6692740</v>
+        <v>6692719</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2964,12 +2642,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,15 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112657452</v>
+        <v>95269649</v>
       </c>
       <c r="B22" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,37 +2685,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571481</v>
+        <v>571222</v>
       </c>
       <c r="R22" t="n">
-        <v>6692728</v>
+        <v>6692784</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3066,12 +2741,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,65 +2783,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112657491</v>
+        <v>95336431</v>
       </c>
       <c r="B23" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571534</v>
+        <v>571308</v>
       </c>
       <c r="R23" t="n">
-        <v>6692641</v>
+        <v>6692811</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3180,12 +2849,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,7 +2873,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3213,37 +2891,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112657512</v>
+        <v>117182945</v>
       </c>
       <c r="B24" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3253,10 +2926,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571460</v>
+        <v>571282</v>
       </c>
       <c r="R24" t="n">
-        <v>6692770</v>
+        <v>6692821</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3283,12 +2956,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,37 +2988,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112657446</v>
+        <v>112657452</v>
       </c>
       <c r="B25" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3023,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571241</v>
+        <v>571481</v>
       </c>
       <c r="R25" t="n">
-        <v>6692737</v>
+        <v>6692729</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3417,37 +3085,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112657442</v>
+        <v>112657453</v>
       </c>
       <c r="B26" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3457,10 +3120,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571236</v>
+        <v>571461</v>
       </c>
       <c r="R26" t="n">
-        <v>6692738</v>
+        <v>6692740</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3519,37 +3182,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112657510</v>
+        <v>112657455</v>
       </c>
       <c r="B27" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3559,10 +3217,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571526</v>
+        <v>571472</v>
       </c>
       <c r="R27" t="n">
-        <v>6692648</v>
+        <v>6692743</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3621,15 +3279,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112657455</v>
+        <v>117182942</v>
       </c>
       <c r="B28" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3661,10 +3314,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571471</v>
+        <v>571402</v>
       </c>
       <c r="R28" t="n">
-        <v>6692744</v>
+        <v>6692830</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3691,12 +3344,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,15 +3376,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112657492</v>
+        <v>112657518</v>
       </c>
       <c r="B29" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,46 +3387,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571383</v>
+        <v>571458</v>
       </c>
       <c r="R29" t="n">
-        <v>6692834</v>
+        <v>6692769</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3819,7 +3455,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3838,37 +3473,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112657481</v>
+        <v>112657519</v>
       </c>
       <c r="B30" t="n">
-        <v>89717</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3878,10 +3508,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571393</v>
+        <v>571408</v>
       </c>
       <c r="R30" t="n">
-        <v>6692829</v>
+        <v>6692740</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3922,7 +3552,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3941,37 +3570,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112657445</v>
+        <v>112657520</v>
       </c>
       <c r="B31" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3605,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571242</v>
+        <v>571281</v>
       </c>
       <c r="R31" t="n">
-        <v>6692726</v>
+        <v>6692905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4043,37 +3667,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112657517</v>
+        <v>112657521</v>
       </c>
       <c r="B32" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4083,10 +3702,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571519</v>
+        <v>571266</v>
       </c>
       <c r="R32" t="n">
-        <v>6692640</v>
+        <v>6692897</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4145,37 +3764,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112657447</v>
+        <v>112657522</v>
       </c>
       <c r="B33" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4185,10 +3799,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571236</v>
+        <v>571264</v>
       </c>
       <c r="R33" t="n">
-        <v>6692730</v>
+        <v>6692907</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4247,37 +3861,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112657444</v>
+        <v>112657523</v>
       </c>
       <c r="B34" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>571259</v>
+        <v>571253</v>
       </c>
       <c r="R34" t="n">
-        <v>6692742</v>
+        <v>6692908</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4349,58 +3958,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112657471</v>
+        <v>112657526</v>
       </c>
       <c r="B35" t="n">
-        <v>55842</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571275</v>
+        <v>571259</v>
       </c>
       <c r="R35" t="n">
-        <v>6692685</v>
+        <v>6692918</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4459,37 +4055,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112657441</v>
+        <v>112657528</v>
       </c>
       <c r="B36" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4499,10 +4090,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571383</v>
+        <v>571262</v>
       </c>
       <c r="R36" t="n">
-        <v>6692827</v>
+        <v>6692918</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4561,50 +4152,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112657443</v>
+        <v>112792845</v>
       </c>
       <c r="B37" t="n">
-        <v>94555</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Igeltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>571258</v>
+        <v>571344</v>
       </c>
       <c r="R37" t="n">
-        <v>6692748</v>
+        <v>6692780</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4631,12 +4217,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4651,74 +4237,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112657495</v>
+        <v>112657516</v>
       </c>
       <c r="B38" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571196</v>
+        <v>571396</v>
       </c>
       <c r="R38" t="n">
-        <v>6692766</v>
+        <v>6692664</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4759,7 +4328,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4778,53 +4346,56 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112657519</v>
+        <v>96490131</v>
       </c>
       <c r="B39" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Igeltjärn ö, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571407</v>
+        <v>571233</v>
       </c>
       <c r="R39" t="n">
-        <v>6692740</v>
+        <v>6692693</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4848,12 +4419,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>födosökningshål i torrgran, stubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4868,27 +4454,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisabeth Norman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisabeth Norman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112657520</v>
+        <v>112657465</v>
       </c>
       <c r="B40" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,34 +4477,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571280</v>
+        <v>571408</v>
       </c>
       <c r="R40" t="n">
-        <v>6692905</v>
+        <v>6692740</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4982,50 +4571,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112657453</v>
+        <v>112657467</v>
       </c>
       <c r="B41" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571461</v>
+        <v>571266</v>
       </c>
       <c r="R41" t="n">
-        <v>6692740</v>
+        <v>6692897</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5084,50 +4676,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112657509</v>
+        <v>112657470</v>
       </c>
       <c r="B42" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571277</v>
+        <v>571575</v>
       </c>
       <c r="R42" t="n">
-        <v>6692745</v>
+        <v>6692547</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5186,50 +4781,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112657518</v>
+        <v>112657471</v>
       </c>
       <c r="B43" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571458</v>
+        <v>571275</v>
       </c>
       <c r="R43" t="n">
-        <v>6692770</v>
+        <v>6692685</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5288,37 +4886,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112657511</v>
+        <v>112657539</v>
       </c>
       <c r="B44" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5328,10 +4921,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571466</v>
+        <v>571264</v>
       </c>
       <c r="R44" t="n">
-        <v>6692762</v>
+        <v>6692910</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5390,50 +4983,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112657513</v>
+        <v>112792850</v>
       </c>
       <c r="B45" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sindertäkten, Dlr</t>
+          <t>Igeltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571387</v>
+        <v>571311</v>
       </c>
       <c r="R45" t="n">
-        <v>6692747</v>
+        <v>6692751</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5460,12 +5048,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5480,74 +5068,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112657496</v>
+        <v>117182957</v>
       </c>
       <c r="B46" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571184</v>
+        <v>571301</v>
       </c>
       <c r="R46" t="n">
-        <v>6692752</v>
+        <v>6692786</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5574,12 +5145,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5588,7 +5159,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5607,37 +5177,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112657458</v>
+        <v>112657441</v>
       </c>
       <c r="B47" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5647,10 +5212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571231</v>
+        <v>571383</v>
       </c>
       <c r="R47" t="n">
-        <v>6692721</v>
+        <v>6692827</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5709,15 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112792850</v>
+        <v>112792824</v>
       </c>
       <c r="B48" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5725,24 +5285,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Igeltjärnen, Dlr</t>
@@ -5752,7 +5317,7 @@
         <v>571311</v>
       </c>
       <c r="R48" t="n">
-        <v>6692751</v>
+        <v>6692752</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5793,6 +5358,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5811,53 +5377,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112792830</v>
+        <v>95269698</v>
       </c>
       <c r="B49" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Igeltjärnen, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571311</v>
+        <v>571217</v>
       </c>
       <c r="R49" t="n">
-        <v>6692752</v>
+        <v>6692772</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5881,12 +5448,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5901,65 +5478,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112792845</v>
+        <v>95269753</v>
       </c>
       <c r="B50" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Igeltjärnen, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571344</v>
+        <v>571244</v>
       </c>
       <c r="R50" t="n">
-        <v>6692780</v>
+        <v>6692774</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5983,12 +5557,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>200-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6003,70 +5592,66 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112792824</v>
+        <v>95269787</v>
       </c>
       <c r="B51" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Igeltjärnen, Dlr</t>
+          <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571311</v>
+        <v>571260</v>
       </c>
       <c r="R51" t="n">
-        <v>6692752</v>
+        <v>6692753</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6090,12 +5675,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>9 blommor, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6104,34 +5704,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117183010</v>
+        <v>95270240</v>
       </c>
       <c r="B52" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,32 +5750,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571275</v>
+        <v>571344</v>
       </c>
       <c r="R52" t="n">
-        <v>6692802</v>
+        <v>6692748</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6205,12 +5793,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 blommor, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6219,7 +5822,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6238,15 +5840,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117183009</v>
+        <v>95270707</v>
       </c>
       <c r="B53" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6273,30 +5870,24 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571357</v>
+        <v>571551</v>
       </c>
       <c r="R53" t="n">
-        <v>6692841</v>
+        <v>6692659</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6320,12 +5911,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6334,7 +5935,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6353,15 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117183021</v>
+        <v>95336369</v>
       </c>
       <c r="B54" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6386,32 +5981,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571379</v>
+        <v>571371</v>
       </c>
       <c r="R54" t="n">
-        <v>6692820</v>
+        <v>6692775</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6435,12 +6024,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>30-tal bladrosetter, 1 blomma</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6449,7 +6053,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6468,53 +6071,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117182941</v>
+        <v>95336462</v>
       </c>
       <c r="B55" t="n">
-        <v>95350</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571388</v>
+        <v>571236</v>
       </c>
       <c r="R55" t="n">
-        <v>6692681</v>
+        <v>6692772</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6538,12 +6138,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6570,15 +6185,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117183008</v>
+        <v>112657490</v>
       </c>
       <c r="B56" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6622,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571337</v>
+        <v>571273</v>
       </c>
       <c r="R56" t="n">
-        <v>6692709</v>
+        <v>6692739</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6652,12 +6262,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6685,50 +6295,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117182957</v>
+        <v>112657491</v>
       </c>
       <c r="B57" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571301</v>
+        <v>571534</v>
       </c>
       <c r="R57" t="n">
-        <v>6692786</v>
+        <v>6692641</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6755,12 +6372,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,6 +6386,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6787,15 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117183011</v>
+        <v>112657492</v>
       </c>
       <c r="B58" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6822,7 +6435,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6839,10 +6452,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571279</v>
+        <v>571384</v>
       </c>
       <c r="R58" t="n">
-        <v>6692804</v>
+        <v>6692834</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6869,12 +6482,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,50 +6515,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117182940</v>
+        <v>112657495</v>
       </c>
       <c r="B59" t="n">
-        <v>95350</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571250</v>
+        <v>571196</v>
       </c>
       <c r="R59" t="n">
-        <v>6692733</v>
+        <v>6692766</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6972,12 +6592,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6986,6 +6606,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7004,15 +6625,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117182947</v>
+        <v>112657496</v>
       </c>
       <c r="B60" t="n">
-        <v>97802</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7037,17 +6653,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sindertäkten, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571335</v>
+        <v>571184</v>
       </c>
       <c r="R60" t="n">
-        <v>6692772</v>
+        <v>6692752</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7074,12 +6702,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7088,6 +6716,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7106,37 +6735,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117182944</v>
+        <v>112657509</v>
       </c>
       <c r="B61" t="n">
-        <v>90465</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +6770,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>571434</v>
+        <v>571276</v>
       </c>
       <c r="R61" t="n">
-        <v>6692719</v>
+        <v>6692745</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7176,12 +6800,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7208,37 +6832,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117182943</v>
+        <v>112657510</v>
       </c>
       <c r="B62" t="n">
-        <v>90465</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7248,10 +6867,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>571388</v>
+        <v>571526</v>
       </c>
       <c r="R62" t="n">
-        <v>6692669</v>
+        <v>6692648</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7278,12 +6897,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7310,37 +6929,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117182952</v>
+        <v>112657511</v>
       </c>
       <c r="B63" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7350,10 +6964,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>571526</v>
+        <v>571466</v>
       </c>
       <c r="R63" t="n">
-        <v>6692643</v>
+        <v>6692763</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7380,12 +6994,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7412,37 +7026,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117182945</v>
+        <v>112657512</v>
       </c>
       <c r="B64" t="n">
-        <v>90519</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7452,10 +7061,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>571282</v>
+        <v>571460</v>
       </c>
       <c r="R64" t="n">
-        <v>6692821</v>
+        <v>6692769</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7482,12 +7091,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7511,6 +7120,859 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>112657513</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>571386</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6692748</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>117182947</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>571335</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6692772</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>117183008</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>571337</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6692709</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>117183009</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>571357</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6692841</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>117183010</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>571275</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6692802</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>117183011</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>571279</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6692804</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>117183021</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>571379</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6692820</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>95269633</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sindertäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>571219</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6692784</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55899-2023 artfynd.xlsx
+++ b/artfynd/A 55899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95271571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95271671</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95274252</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95337982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481182</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481186</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657442</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657443</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657445</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657446</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657447</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792830</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182940</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2260,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2283,6 +2363,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657481</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2380,6 +2465,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657458</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2477,6 +2567,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657461</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2574,6 +2669,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182943</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2671,6 +2771,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182944</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2780,6 +2885,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269649</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2888,6 +2998,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95336431</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2985,6 +3100,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182945</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3082,6 +3202,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657452</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3179,6 +3304,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657453</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3276,6 +3406,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657455</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3373,6 +3508,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182942</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3470,6 +3610,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657518</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3567,6 +3712,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657519</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3664,6 +3814,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657520</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3761,6 +3916,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657521</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3858,6 +4018,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657522</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3955,6 +4120,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657523</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4052,6 +4222,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657526</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4149,6 +4324,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4246,6 +4426,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792845</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4343,6 +4528,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657516</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4463,6 +4653,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96490131</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4568,6 +4763,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657465</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4673,6 +4873,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657467</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4778,6 +4983,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657470</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4883,6 +5093,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657471</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4980,6 +5195,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657539</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5077,6 +5297,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792850</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5174,6 +5399,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182957</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5271,6 +5501,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657441</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5374,6 +5609,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792824</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5487,6 +5727,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269698</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5601,6 +5846,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269753</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5719,6 +5969,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269787</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5837,6 +6092,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95270240</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5950,6 +6210,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95270707</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6068,6 +6333,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95336369</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6182,6 +6452,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95336462</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6292,6 +6567,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657490</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6402,6 +6682,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657491</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6512,6 +6797,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657492</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6622,6 +6912,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657495</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6732,6 +7027,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657496</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6829,6 +7129,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657509</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6926,6 +7231,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657510</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7023,6 +7333,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657511</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7120,6 +7435,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657512</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7217,6 +7537,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657513</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7314,6 +7639,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117182947</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7424,6 +7754,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117183008</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7534,6 +7869,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117183009</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7644,6 +7984,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117183010</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7754,6 +8099,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117183011</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7864,6 +8214,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117183021</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7973,8 +8328,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>